--- a/AAII_Financials/Yearly/ARES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARES_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>ARES</t>
   </si>
@@ -732,25 +732,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5601500</v>
+        <v>4834000</v>
       </c>
       <c r="E8" s="3">
-        <v>3884800</v>
+        <v>2906500</v>
       </c>
       <c r="F8" s="3">
-        <v>3631900</v>
+        <v>2771000</v>
       </c>
       <c r="G8" s="3">
-        <v>3055400</v>
+        <v>2572700</v>
       </c>
       <c r="H8" s="3">
-        <v>4212100</v>
+        <v>3917300</v>
       </c>
       <c r="I8" s="3">
-        <v>1764000</v>
+        <v>1452800</v>
       </c>
       <c r="J8" s="3">
-        <v>1765400</v>
+        <v>1468000</v>
       </c>
       <c r="K8" s="3">
         <v>958500</v>
@@ -782,26 +782,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>3554800</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2143200</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2086900</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1811200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2836500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1171400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1150500</v>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K9" s="3">
         <v>600600</v>
@@ -834,25 +834,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2046700</v>
+        <v>4834000</v>
       </c>
       <c r="E10" s="3">
-        <v>1741600</v>
+        <v>2906500</v>
       </c>
       <c r="F10" s="3">
-        <v>1545000</v>
+        <v>2771000</v>
       </c>
       <c r="G10" s="3">
-        <v>1244300</v>
+        <v>2572700</v>
       </c>
       <c r="H10" s="3">
-        <v>1375600</v>
+        <v>3917300</v>
       </c>
       <c r="I10" s="3">
-        <v>592700</v>
+        <v>1452800</v>
       </c>
       <c r="J10" s="3">
-        <v>614900</v>
+        <v>1468000</v>
       </c>
       <c r="K10" s="3">
         <v>357800</v>
@@ -1008,22 +1008,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-751200</v>
+        <v>-716800</v>
       </c>
       <c r="E14" s="3">
-        <v>-283500</v>
+        <v>-258900</v>
       </c>
       <c r="F14" s="3">
-        <v>-254200</v>
+        <v>-332700</v>
       </c>
       <c r="G14" s="3">
-        <v>309700</v>
+        <v>127300</v>
       </c>
       <c r="H14" s="3">
-        <v>-29500</v>
+        <v>-30900</v>
       </c>
       <c r="I14" s="3">
-        <v>105900</v>
+        <v>116000</v>
       </c>
       <c r="J14" s="3">
         <v>-4700</v>
@@ -1059,16 +1059,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>240800</v>
+        <v>243100</v>
       </c>
       <c r="E15" s="3">
-        <v>149700</v>
+        <v>158600</v>
       </c>
       <c r="F15" s="3">
-        <v>153000</v>
+        <v>231700</v>
       </c>
       <c r="G15" s="3">
-        <v>159700</v>
+        <v>341300</v>
       </c>
       <c r="H15" s="3">
         <v>113300</v>
@@ -1077,7 +1077,7 @@
         <v>41200</v>
       </c>
       <c r="J15" s="3">
-        <v>19500</v>
+        <v>39500</v>
       </c>
       <c r="K15" s="3">
         <v>28500</v>
@@ -1128,22 +1128,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4601300</v>
+        <v>4568300</v>
       </c>
       <c r="E17" s="3">
-        <v>2891600</v>
+        <v>2867100</v>
       </c>
       <c r="F17" s="3">
-        <v>2711800</v>
+        <v>2790500</v>
       </c>
       <c r="G17" s="3">
-        <v>2361200</v>
+        <v>2542800</v>
       </c>
       <c r="H17" s="3">
         <v>3343200</v>
       </c>
       <c r="I17" s="3">
-        <v>1450500</v>
+        <v>1439400</v>
       </c>
       <c r="J17" s="3">
         <v>1442800</v>
@@ -1179,25 +1179,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1000200</v>
+        <v>265800</v>
       </c>
       <c r="E18" s="3">
-        <v>993100</v>
+        <v>39300</v>
       </c>
       <c r="F18" s="3">
-        <v>920100</v>
+        <v>-19500</v>
       </c>
       <c r="G18" s="3">
-        <v>694200</v>
+        <v>29900</v>
       </c>
       <c r="H18" s="3">
-        <v>868900</v>
+        <v>574100</v>
       </c>
       <c r="I18" s="3">
-        <v>313600</v>
+        <v>13500</v>
       </c>
       <c r="J18" s="3">
-        <v>322600</v>
+        <v>25200</v>
       </c>
       <c r="K18" s="3">
         <v>88100</v>
@@ -1302,25 +1302,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>921300</v>
+        <v>189200</v>
       </c>
       <c r="E21" s="3">
-        <v>1143400</v>
+        <v>198500</v>
       </c>
       <c r="F21" s="3">
-        <v>1077900</v>
+        <v>217000</v>
       </c>
       <c r="G21" s="3">
-        <v>867100</v>
+        <v>384400</v>
       </c>
       <c r="H21" s="3">
-        <v>996600</v>
+        <v>701800</v>
       </c>
       <c r="I21" s="3">
-        <v>366100</v>
+        <v>66000</v>
       </c>
       <c r="J21" s="3">
-        <v>334300</v>
+        <v>56800</v>
       </c>
       <c r="K21" s="3">
         <v>115800</v>
@@ -1352,26 +1352,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>767500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>978300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>860900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>482700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>294800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>311200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>297400</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>244300</v>
@@ -1404,22 +1404,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1286900</v>
+        <v>1285500</v>
       </c>
       <c r="E23" s="3">
-        <v>1275400</v>
+        <v>1275200</v>
       </c>
       <c r="F23" s="3">
-        <v>1333100</v>
+        <v>1332800</v>
       </c>
       <c r="G23" s="3">
-        <v>510800</v>
+        <v>511700</v>
       </c>
       <c r="H23" s="3">
-        <v>1065700</v>
+        <v>1067000</v>
       </c>
       <c r="I23" s="3">
-        <v>379500</v>
+        <v>380500</v>
       </c>
       <c r="J23" s="3">
         <v>425200</v>
@@ -1557,22 +1557,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1088400</v>
+        <v>1087000</v>
       </c>
       <c r="E26" s="3">
-        <v>1110700</v>
+        <v>1110600</v>
       </c>
       <c r="F26" s="3">
-        <v>1160100</v>
+        <v>1159900</v>
       </c>
       <c r="G26" s="3">
-        <v>438900</v>
+        <v>439800</v>
       </c>
       <c r="H26" s="3">
-        <v>918300</v>
+        <v>919600</v>
       </c>
       <c r="I26" s="3">
-        <v>324500</v>
+        <v>325500</v>
       </c>
       <c r="J26" s="3">
         <v>372800</v>
@@ -1608,13 +1608,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>468700</v>
+        <v>383500</v>
       </c>
       <c r="E27" s="3">
-        <v>471700</v>
+        <v>410200</v>
       </c>
       <c r="F27" s="3">
-        <v>495600</v>
+        <v>453000</v>
       </c>
       <c r="G27" s="3">
         <v>153400</v>
@@ -2228,10 +2228,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2282,10 +2282,10 @@
         <v>1071000</v>
       </c>
       <c r="I43" s="3">
-        <v>548400</v>
+        <v>549500</v>
       </c>
       <c r="J43" s="3">
-        <v>374400</v>
+        <v>375000</v>
       </c>
       <c r="K43" s="3">
         <v>293700</v>
@@ -2369,25 +2369,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>470000</v>
+        <v>451800</v>
       </c>
       <c r="E45" s="3">
-        <v>251300</v>
+        <v>247500</v>
       </c>
       <c r="F45" s="3">
-        <v>178100</v>
+        <v>177000</v>
       </c>
       <c r="G45" s="3">
-        <v>136400</v>
+        <v>132200</v>
       </c>
       <c r="H45" s="3">
         <v>86900</v>
       </c>
       <c r="I45" s="3">
-        <v>76900</v>
+        <v>75800</v>
       </c>
       <c r="J45" s="3">
-        <v>69200</v>
+        <v>64500</v>
       </c>
       <c r="K45" s="3">
         <v>51500</v>
@@ -2420,25 +2420,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3367000</v>
+        <v>3348700</v>
       </c>
       <c r="E46" s="3">
-        <v>4250000</v>
+        <v>4246300</v>
       </c>
       <c r="F46" s="3">
-        <v>2772100</v>
+        <v>2771000</v>
       </c>
       <c r="G46" s="3">
-        <v>2203600</v>
+        <v>2199400</v>
       </c>
       <c r="H46" s="3">
-        <v>2556500</v>
+        <v>2550800</v>
       </c>
       <c r="I46" s="3">
-        <v>1688900</v>
+        <v>1687500</v>
       </c>
       <c r="J46" s="3">
-        <v>1188300</v>
+        <v>1184300</v>
       </c>
       <c r="K46" s="3">
         <v>840100</v>
@@ -2474,16 +2474,16 @@
         <v>18353300</v>
       </c>
       <c r="E47" s="3">
-        <v>17382600</v>
+        <v>16831800</v>
       </c>
       <c r="F47" s="3">
-        <v>19226500</v>
+        <v>18703500</v>
       </c>
       <c r="G47" s="3">
-        <v>17179400</v>
+        <v>16166000</v>
       </c>
       <c r="H47" s="3">
-        <v>16500900</v>
+        <v>15500700</v>
       </c>
       <c r="I47" s="3">
         <v>12559900</v>
@@ -2726,25 +2726,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>239900</v>
+        <v>263900</v>
       </c>
       <c r="E52" s="3">
-        <v>177500</v>
+        <v>736900</v>
       </c>
       <c r="F52" s="3">
-        <v>152100</v>
+        <v>680500</v>
       </c>
       <c r="G52" s="3">
-        <v>101900</v>
+        <v>1125000</v>
       </c>
       <c r="H52" s="3">
-        <v>52400</v>
+        <v>1063600</v>
       </c>
       <c r="I52" s="3">
-        <v>30600</v>
+        <v>41500</v>
       </c>
       <c r="J52" s="3">
-        <v>21700</v>
+        <v>32000</v>
       </c>
       <c r="K52" s="3">
         <v>28200</v>
@@ -2921,13 +2921,13 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1470000</v>
+        <v>687100</v>
       </c>
       <c r="E57" s="3">
-        <v>1014600</v>
+        <v>988500</v>
       </c>
       <c r="F57" s="3">
-        <v>896700</v>
+        <v>894100</v>
       </c>
       <c r="G57" s="3">
         <v>695200</v>
@@ -2972,25 +2972,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1452600</v>
+        <v>1460200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F58" s="3">
-        <v>125200</v>
+        <v>278100</v>
       </c>
       <c r="G58" s="3">
-        <v>93000</v>
+        <v>96700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>92800</v>
       </c>
       <c r="I58" s="3">
-        <v>32500</v>
+        <v>105600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>76400</v>
       </c>
       <c r="K58" s="3">
         <v>43600</v>
@@ -3023,25 +3023,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>584800</v>
+        <v>7800</v>
       </c>
       <c r="E59" s="3">
-        <v>407100</v>
+        <v>29300</v>
       </c>
       <c r="F59" s="3">
-        <v>205600</v>
+        <v>7800</v>
       </c>
       <c r="G59" s="3">
-        <v>141800</v>
+        <v>9200</v>
       </c>
       <c r="H59" s="3">
-        <v>121800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>64100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>31400</v>
+        <v>45900</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>28300</v>
@@ -3074,25 +3074,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7138100</v>
+        <v>5777900</v>
       </c>
       <c r="E60" s="3">
-        <v>4318500</v>
+        <v>3890200</v>
       </c>
       <c r="F60" s="3">
-        <v>4062900</v>
+        <v>4007400</v>
       </c>
       <c r="G60" s="3">
-        <v>3843600</v>
+        <v>3705600</v>
       </c>
       <c r="H60" s="3">
-        <v>4168100</v>
+        <v>4139000</v>
       </c>
       <c r="I60" s="3">
-        <v>1714500</v>
+        <v>1723500</v>
       </c>
       <c r="J60" s="3">
-        <v>1570700</v>
+        <v>1615700</v>
       </c>
       <c r="K60" s="3">
         <v>1411400</v>
@@ -3131,19 +3131,19 @@
         <v>13148000</v>
       </c>
       <c r="F61" s="3">
-        <v>15630700</v>
+        <v>15491300</v>
       </c>
       <c r="G61" s="3">
-        <v>13241200</v>
+        <v>13256700</v>
       </c>
       <c r="H61" s="3">
-        <v>12495200</v>
+        <v>12423700</v>
       </c>
       <c r="I61" s="3">
-        <v>10872000</v>
+        <v>10800500</v>
       </c>
       <c r="J61" s="3">
-        <v>8568100</v>
+        <v>8496600</v>
       </c>
       <c r="K61" s="3">
         <v>7324700</v>
@@ -3176,25 +3176,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>14000</v>
+        <v>1359300</v>
       </c>
       <c r="E62" s="3">
-        <v>13700</v>
+        <v>433600</v>
       </c>
       <c r="F62" s="3">
-        <v>6000</v>
+        <v>200800</v>
       </c>
       <c r="G62" s="3">
-        <v>4300</v>
+        <v>126800</v>
       </c>
       <c r="H62" s="3">
-        <v>21400</v>
+        <v>121900</v>
       </c>
       <c r="I62" s="3">
-        <v>5600</v>
+        <v>68100</v>
       </c>
       <c r="J62" s="3">
-        <v>11400</v>
+        <v>37900</v>
       </c>
       <c r="K62" s="3">
         <v>18700</v>
@@ -4090,16 +4090,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>47400</v>
+        <v>49700</v>
       </c>
       <c r="E83" s="3">
-        <v>33400</v>
+        <v>42300</v>
       </c>
       <c r="F83" s="3">
-        <v>27000</v>
+        <v>105700</v>
       </c>
       <c r="G83" s="3">
-        <v>26100</v>
+        <v>207700</v>
       </c>
       <c r="H83" s="3">
         <v>22000</v>
@@ -4108,7 +4108,7 @@
         <v>16700</v>
       </c>
       <c r="J83" s="3">
-        <v>16100</v>
+        <v>36100</v>
       </c>
       <c r="K83" s="3">
         <v>19500</v>
@@ -4693,25 +4693,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>1756700</v>
       </c>
       <c r="E96" s="3">
-        <v>783200</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>599900</v>
+        <v>1030700</v>
       </c>
       <c r="G96" s="3">
         <v>447600</v>
       </c>
       <c r="H96" s="3">
-        <v>324300</v>
+        <v>593500</v>
       </c>
       <c r="I96" s="3">
-        <v>231400</v>
+        <v>446800</v>
       </c>
       <c r="J96" s="3">
-        <v>148700</v>
+        <v>323700</v>
       </c>
       <c r="K96" s="3">
         <v>134800</v>
